--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -1401,7 +1401,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -1421,7 +1421,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>19</v>
@@ -1441,7 +1441,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1461,7 +1461,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -1481,7 +1481,7 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -1501,7 +1501,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1541,7 +1541,7 @@
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>24</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1581,7 +1581,7 @@
         <v>24</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>19</v>
@@ -1601,7 +1601,7 @@
         <v>24</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>19</v>
@@ -1621,7 +1621,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>19</v>
@@ -1661,7 +1661,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>19</v>
@@ -1681,7 +1681,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>19</v>
@@ -1741,7 +1741,7 @@
         <v>29</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>19</v>
@@ -1761,7 +1761,7 @@
         <v>29</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1781,7 +1781,7 @@
         <v>29</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1801,7 +1801,7 @@
         <v>29</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -1841,7 +1841,7 @@
         <v>32</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -1861,7 +1861,7 @@
         <v>32</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -1881,7 +1881,7 @@
         <v>32</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>32</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>19</v>
@@ -1921,7 +1921,7 @@
         <v>32</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>19</v>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="133">
   <si>
     <t/>
   </si>
@@ -148,6 +148,15 @@
     <t>12</t>
   </si>
   <si>
+    <t>20142129</t>
+  </si>
+  <si>
+    <t>CORNETTO MATCHA STRW</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20092895</t>
   </si>
   <si>
@@ -398,9 +407,6 @@
   </si>
   <si>
     <t>WALL WHT ROSE PHTCRD</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>RT</t>
@@ -796,13 +802,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -1118,21 +1124,21 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1141,7 +1147,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1149,10 +1155,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1161,18 +1167,18 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1181,7 +1187,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>19</v>
@@ -1189,10 +1195,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1201,7 +1207,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
@@ -1209,10 +1215,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1221,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
@@ -1229,10 +1235,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1241,7 +1247,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
@@ -1249,10 +1255,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1261,7 +1267,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>19</v>
@@ -1269,10 +1275,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1281,7 +1287,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>19</v>
@@ -1289,10 +1295,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1301,7 +1307,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>19</v>
@@ -1309,19 +1315,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>19</v>
@@ -1329,10 +1335,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1341,18 +1347,18 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1361,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1369,10 +1375,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1381,7 +1387,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1389,10 +1395,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1401,18 +1407,18 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1421,7 +1427,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>19</v>
@@ -1429,10 +1435,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1441,7 +1447,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1449,10 +1455,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1461,7 +1467,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -1469,10 +1475,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1481,7 +1487,7 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -1489,10 +1495,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1501,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1509,19 +1515,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1529,10 +1535,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1541,18 +1547,18 @@
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1561,7 +1567,7 @@
         <v>24</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1569,10 +1575,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1581,18 +1587,18 @@
         <v>24</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1601,7 +1607,7 @@
         <v>24</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>19</v>
@@ -1609,10 +1615,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1621,7 +1627,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>19</v>
@@ -1629,30 +1635,30 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1661,18 +1667,18 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1681,7 +1687,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>19</v>
@@ -1689,30 +1695,30 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1721,18 +1727,18 @@
         <v>29</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1741,18 +1747,18 @@
         <v>29</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1761,7 +1767,7 @@
         <v>29</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1769,10 +1775,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1781,7 +1787,7 @@
         <v>29</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1789,10 +1795,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -1801,7 +1807,7 @@
         <v>29</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -1809,30 +1815,30 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -1841,7 +1847,7 @@
         <v>32</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -1849,10 +1855,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -1861,7 +1867,7 @@
         <v>32</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -1869,10 +1875,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -1881,7 +1887,7 @@
         <v>32</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -1889,10 +1895,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -1901,18 +1907,18 @@
         <v>32</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -1921,7 +1927,7 @@
         <v>32</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>19</v>
@@ -1929,22 +1935,42 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>130</v>
+      <c r="F58" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="134">
   <si>
     <t/>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>WALL WHT ROSE PHTCRD</t>
+  </si>
+  <si>
+    <t>998</t>
   </si>
   <si>
     <t>RT</t>
@@ -808,7 +811,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -1964,13 +1967,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="122">
   <si>
     <t/>
   </si>
@@ -31,21 +31,21 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20094387</t>
+  </si>
+  <si>
+    <t>CRNETTO SLV QUEEN108</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>20072317</t>
   </si>
   <si>
     <t>CORNETTO OREO 110</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20094387</t>
-  </si>
-  <si>
-    <t>CRNETTO SLV QUEEN108</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -61,31 +61,277 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
+    <t>20142423</t>
+  </si>
+  <si>
+    <t>MAGNUM PISTACHIO80</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20035518</t>
+  </si>
+  <si>
+    <t>WALLS P/P RAINBW P50</t>
+  </si>
+  <si>
+    <t>20136302</t>
+  </si>
+  <si>
+    <t>WALLS CRNTO MLK.BR80</t>
+  </si>
+  <si>
+    <t>20136404</t>
+  </si>
+  <si>
+    <t>WALLS TWST GRP LYC55</t>
+  </si>
+  <si>
+    <t>20136702</t>
+  </si>
+  <si>
+    <t>MAGNUM CF.AU LAIT 80</t>
+  </si>
+  <si>
+    <t>20140723</t>
+  </si>
+  <si>
+    <t>PADDLE POP FRT TOWER</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20140366</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO LAVA 65</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20142129</t>
+  </si>
+  <si>
+    <t>CORNETTO MATCHA STRW</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20137106</t>
+  </si>
+  <si>
+    <t>PADDLE POP JG.JLY 60</t>
+  </si>
+  <si>
+    <t>20138191</t>
+  </si>
+  <si>
+    <t>WALL FST POP STR</t>
+  </si>
+  <si>
+    <t>20140730</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO BROWNIE</t>
+  </si>
+  <si>
+    <t>20141544</t>
+  </si>
+  <si>
+    <t>WALLS CLP PEACHMG100</t>
+  </si>
+  <si>
+    <t>20141545</t>
+  </si>
+  <si>
+    <t>WALLS CLP STWPINE100</t>
+  </si>
+  <si>
+    <t>20134926</t>
+  </si>
+  <si>
+    <t>WALL ICE CRM OREO 80</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20125168</t>
+  </si>
+  <si>
+    <t>WALL FST POP VN&amp;CR64</t>
+  </si>
+  <si>
+    <t>20139189</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO P&amp;L 65</t>
+  </si>
+  <si>
+    <t>10037632</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST CKLT.65</t>
+  </si>
+  <si>
+    <t>10037640</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST VNILA65</t>
+  </si>
+  <si>
+    <t>20139460</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO HZL 108</t>
+  </si>
+  <si>
+    <t>20140087</t>
+  </si>
+  <si>
+    <t>WALLS FEAST MAX CHO</t>
+  </si>
+  <si>
+    <t>20141200</t>
+  </si>
+  <si>
+    <t>WALLS BALL STRW GUAV</t>
+  </si>
+  <si>
+    <t>20141201</t>
+  </si>
+  <si>
+    <t>WALLS BALL GRAPE</t>
+  </si>
+  <si>
+    <t>20129821</t>
+  </si>
+  <si>
+    <t>MAGNUM MATCHA.CRBL80</t>
+  </si>
+  <si>
+    <t>20032368</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM ALMD80</t>
+  </si>
+  <si>
+    <t>20032366</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM CLAS80</t>
+  </si>
+  <si>
+    <t>20134689</t>
+  </si>
+  <si>
+    <t>MAGNUM MNGO YOGHRT80</t>
+  </si>
+  <si>
+    <t>20138475</t>
+  </si>
+  <si>
+    <t>WALLS MGNUM STRW PAN</t>
+  </si>
+  <si>
+    <t>20054385</t>
+  </si>
+  <si>
+    <t>WALLS NEO EXT.CRM350</t>
+  </si>
+  <si>
+    <t>20137108</t>
+  </si>
+  <si>
+    <t>WALLS TROPCL DL 350</t>
+  </si>
+  <si>
+    <t>20140732</t>
+  </si>
+  <si>
+    <t>WALLS MATCHA STW 350</t>
+  </si>
+  <si>
+    <t>20138583</t>
+  </si>
+  <si>
+    <t>WALLS OREO MINI 6S</t>
+  </si>
+  <si>
+    <t>20136391</t>
+  </si>
+  <si>
+    <t>WALLS POPLRE MANGO90</t>
+  </si>
+  <si>
+    <t>20140731</t>
+  </si>
+  <si>
+    <t>WALLS AVOCDO BRW 350</t>
+  </si>
+  <si>
+    <t>20117569</t>
+  </si>
+  <si>
+    <t>MINI CRNTTO OREO 12S</t>
+  </si>
+  <si>
+    <t>20042833</t>
+  </si>
+  <si>
+    <t>WALL MN CORNT TR&amp;D/C</t>
+  </si>
+  <si>
+    <t>20138847</t>
+  </si>
+  <si>
+    <t>MAGNUM MINI CAS 6S</t>
+  </si>
+  <si>
+    <t>20115639</t>
+  </si>
+  <si>
+    <t>WALLS OREO VNL90</t>
+  </si>
+  <si>
+    <t>10005038</t>
+  </si>
+  <si>
+    <t>WALLS PPL CHO-VNL 90</t>
+  </si>
+  <si>
+    <t>10005039</t>
+  </si>
+  <si>
+    <t>WALLS PPL STW-VNL 90</t>
+  </si>
+  <si>
+    <t>20008252</t>
+  </si>
+  <si>
+    <t>WALL'S P/P SHAKY 140</t>
+  </si>
+  <si>
+    <t>20140183</t>
+  </si>
+  <si>
+    <t>WALLS X PC PSL 90ML</t>
+  </si>
+  <si>
     <t>20133505</t>
   </si>
   <si>
     <t>CRNTTO RS CHO CHS134</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20100007</t>
-  </si>
-  <si>
-    <t>CORNETTO STRW&amp;VAN 80</t>
-  </si>
-  <si>
-    <t>20035518</t>
-  </si>
-  <si>
-    <t>WALLS P/P RAINBW P50</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>998</t>
   </si>
   <si>
     <t>20133149</t>
@@ -94,322 +340,40 @@
     <t>PAD.POP UPIN&amp;IPIN 60</t>
   </si>
   <si>
-    <t>20136302</t>
-  </si>
-  <si>
-    <t>WALLS CRNTO MLK.BR80</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20136404</t>
-  </si>
-  <si>
-    <t>WALLS TWST GRP LYC55</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>20136703</t>
   </si>
   <si>
     <t>CRNETTO YGRT BRY 108</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20136702</t>
-  </si>
-  <si>
-    <t>MAGNUM CF.AU LAIT 80</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20140366</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO LAVA 65</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20140723</t>
-  </si>
-  <si>
-    <t>PADDLE POP FRT TOWER</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20142129</t>
-  </si>
-  <si>
-    <t>CORNETTO MATCHA STRW</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20092895</t>
-  </si>
-  <si>
-    <t>WALLS PP CHO LAVA 50</t>
-  </si>
-  <si>
-    <t>20097405</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO MNGA 65</t>
-  </si>
-  <si>
     <t>20134533</t>
   </si>
   <si>
     <t>PADDLE POP MINION 42</t>
   </si>
   <si>
-    <t>20134926</t>
-  </si>
-  <si>
-    <t>WALL ICE CRM OREO 80</t>
-  </si>
-  <si>
-    <t>20137106</t>
-  </si>
-  <si>
-    <t>PADDLE POP JG.JLY 60</t>
-  </si>
-  <si>
     <t>20138193</t>
   </si>
   <si>
     <t>CRNETO APLE CRMBL108</t>
   </si>
   <si>
-    <t>20138191</t>
-  </si>
-  <si>
-    <t>WALL FST POP STR</t>
-  </si>
-  <si>
-    <t>20140730</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO BROWNIE</t>
-  </si>
-  <si>
-    <t>20141545</t>
-  </si>
-  <si>
-    <t>WALLS CLP STWPINE100</t>
-  </si>
-  <si>
-    <t>20141544</t>
-  </si>
-  <si>
-    <t>WALLS CLP PEACHMG100</t>
-  </si>
-  <si>
-    <t>20125168</t>
-  </si>
-  <si>
-    <t>WALL FST POP VN&amp;CR64</t>
-  </si>
-  <si>
-    <t>10037632</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST CKLT.65</t>
-  </si>
-  <si>
     <t>20094824</t>
   </si>
   <si>
     <t>WALLS FEAST D.CHO 75</t>
   </si>
   <si>
-    <t>10037640</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST VNILA65</t>
-  </si>
-  <si>
     <t>20134322</t>
   </si>
   <si>
     <t>WALLS CALIPPO RED100</t>
   </si>
   <si>
-    <t>20139189</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO P&amp;L 65</t>
-  </si>
-  <si>
-    <t>20139460</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO HZL 108</t>
-  </si>
-  <si>
-    <t>20140087</t>
-  </si>
-  <si>
-    <t>WALLS FEAST MAX CHO</t>
-  </si>
-  <si>
-    <t>20141200</t>
-  </si>
-  <si>
-    <t>WALLS BALL STRW GUAV</t>
-  </si>
-  <si>
-    <t>20141201</t>
-  </si>
-  <si>
-    <t>WALLS BALL GRAPE</t>
-  </si>
-  <si>
-    <t>20129821</t>
-  </si>
-  <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
-  </si>
-  <si>
-    <t>20032368</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM ALMD80</t>
-  </si>
-  <si>
-    <t>20032366</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM CLAS80</t>
-  </si>
-  <si>
-    <t>20131617</t>
-  </si>
-  <si>
-    <t>MAGNUM CHOCO.LUXE 80</t>
-  </si>
-  <si>
-    <t>20134689</t>
-  </si>
-  <si>
-    <t>MAGNUM MNGO YOGHRT80</t>
-  </si>
-  <si>
-    <t>20138475</t>
-  </si>
-  <si>
-    <t>WALLS MGNUM STRW PAN</t>
-  </si>
-  <si>
-    <t>20054385</t>
-  </si>
-  <si>
-    <t>WALLS NEO EXT.CRM350</t>
-  </si>
-  <si>
-    <t>20137108</t>
-  </si>
-  <si>
-    <t>WALLS TROPCL DL 350</t>
-  </si>
-  <si>
-    <t>20140732</t>
-  </si>
-  <si>
-    <t>WALLS MATCHA STW 350</t>
-  </si>
-  <si>
-    <t>20042833</t>
-  </si>
-  <si>
-    <t>WALL MN CORNT TR&amp;D/C</t>
-  </si>
-  <si>
-    <t>20117569</t>
-  </si>
-  <si>
-    <t>MINI CRNTTO OREO 12S</t>
-  </si>
-  <si>
-    <t>20136391</t>
-  </si>
-  <si>
-    <t>WALLS POPLRE MANGO90</t>
-  </si>
-  <si>
-    <t>20138583</t>
-  </si>
-  <si>
-    <t>WALLS OREO MINI 6S</t>
-  </si>
-  <si>
-    <t>20138847</t>
-  </si>
-  <si>
-    <t>MAGNUM MINI CAS 6S</t>
-  </si>
-  <si>
-    <t>20140731</t>
-  </si>
-  <si>
-    <t>WALLS AVOCDO BRW 350</t>
-  </si>
-  <si>
-    <t>20115639</t>
-  </si>
-  <si>
-    <t>WALLS OREO VNL90</t>
-  </si>
-  <si>
-    <t>10005038</t>
-  </si>
-  <si>
-    <t>WALLS PPL CHO-VNL 90</t>
-  </si>
-  <si>
-    <t>10005039</t>
-  </si>
-  <si>
-    <t>WALLS PPL STW-VNL 90</t>
-  </si>
-  <si>
-    <t>20008252</t>
-  </si>
-  <si>
-    <t>WALL'S P/P SHAKY 140</t>
-  </si>
-  <si>
-    <t>20137104</t>
-  </si>
-  <si>
-    <t>MAGNUM MINI CMP 6S</t>
-  </si>
-  <si>
-    <t>20140183</t>
-  </si>
-  <si>
-    <t>WALLS X PC PSL 90ML</t>
-  </si>
-  <si>
     <t>20134929</t>
   </si>
   <si>
     <t>WALL WHT ROSE PHTCRD</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>RT</t>
@@ -805,14 +769,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="5" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -953,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,18 +934,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -990,7 +954,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -998,10 +962,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1010,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>19</v>
@@ -1018,10 +982,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1030,7 +994,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>19</v>
@@ -1038,10 +1002,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1050,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>19</v>
@@ -1058,10 +1022,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1070,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>19</v>
@@ -1078,19 +1042,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>19</v>
@@ -1098,19 +1062,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>19</v>
@@ -1118,19 +1082,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>19</v>
@@ -1138,10 +1102,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1150,18 +1114,18 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1170,18 +1134,18 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1190,7 +1154,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>19</v>
@@ -1198,19 +1162,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
@@ -1218,19 +1182,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
@@ -1238,59 +1202,59 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>19</v>
@@ -1298,19 +1262,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>19</v>
@@ -1318,19 +1282,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>19</v>
@@ -1338,10 +1302,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1350,7 +1314,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>19</v>
@@ -1358,39 +1322,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1398,19 +1362,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1418,19 +1382,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>19</v>
@@ -1438,19 +1402,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1458,39 +1422,39 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -1498,19 +1462,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1518,19 +1482,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1538,19 +1502,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -1558,79 +1522,79 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>19</v>
@@ -1638,36 +1602,36 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>4</v>
@@ -1678,99 +1642,99 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1778,19 +1742,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1798,19 +1762,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -1818,19 +1782,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -1838,19 +1802,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -1858,122 +1822,42 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="142">
   <si>
     <t/>
   </si>
@@ -79,174 +79,231 @@
     <t>WALLS P/P RAINBW P50</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20136302</t>
   </si>
   <si>
     <t>WALLS CRNTO MLK.BR80</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>20136404</t>
   </si>
   <si>
     <t>WALLS TWST GRP LYC55</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>20136702</t>
   </si>
   <si>
     <t>MAGNUM CF.AU LAIT 80</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20140723</t>
   </si>
   <si>
     <t>PADDLE POP FRT TOWER</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20140366</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO LAVA 65</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20142129</t>
+  </si>
+  <si>
+    <t>CORNETTO MATCHA STRW</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20137106</t>
+  </si>
+  <si>
+    <t>PADDLE POP JG.JLY 60</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20138191</t>
+  </si>
+  <si>
+    <t>WALL FST POP STR</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20140730</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO BROWNIE</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20141544</t>
+  </si>
+  <si>
+    <t>WALLS CLP PEACHMG100</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20141545</t>
+  </si>
+  <si>
+    <t>WALLS CLP STWPINE100</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20134926</t>
+  </si>
+  <si>
+    <t>WALL ICE CRM OREO 80</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20125168</t>
+  </si>
+  <si>
+    <t>WALL FST POP VN&amp;CR64</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20139189</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO P&amp;L 65</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10037632</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST CKLT.65</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10037640</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST VNILA65</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20139460</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO HZL 108</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20140087</t>
+  </si>
+  <si>
+    <t>WALLS FEAST MAX CHO</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20141200</t>
+  </si>
+  <si>
+    <t>WALLS BALL STRW GUAV</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20141201</t>
+  </si>
+  <si>
+    <t>WALLS BALL GRAPE</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20129821</t>
+  </si>
+  <si>
+    <t>MAGNUM MATCHA.CRBL80</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20032368</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM ALMD80</t>
+  </si>
+  <si>
+    <t>20032366</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM CLAS80</t>
+  </si>
+  <si>
+    <t>20134689</t>
+  </si>
+  <si>
+    <t>MAGNUM MNGO YOGHRT80</t>
+  </si>
+  <si>
+    <t>20138475</t>
+  </si>
+  <si>
+    <t>WALLS MGNUM STRW PAN</t>
+  </si>
+  <si>
+    <t>20054385</t>
+  </si>
+  <si>
+    <t>WALLS NEO EXT.CRM350</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>20140366</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO LAVA 65</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20142129</t>
-  </si>
-  <si>
-    <t>CORNETTO MATCHA STRW</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20137106</t>
-  </si>
-  <si>
-    <t>PADDLE POP JG.JLY 60</t>
-  </si>
-  <si>
-    <t>20138191</t>
-  </si>
-  <si>
-    <t>WALL FST POP STR</t>
-  </si>
-  <si>
-    <t>20140730</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO BROWNIE</t>
-  </si>
-  <si>
-    <t>20141544</t>
-  </si>
-  <si>
-    <t>WALLS CLP PEACHMG100</t>
-  </si>
-  <si>
-    <t>20141545</t>
-  </si>
-  <si>
-    <t>WALLS CLP STWPINE100</t>
-  </si>
-  <si>
-    <t>20134926</t>
-  </si>
-  <si>
-    <t>WALL ICE CRM OREO 80</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20125168</t>
-  </si>
-  <si>
-    <t>WALL FST POP VN&amp;CR64</t>
-  </si>
-  <si>
-    <t>20139189</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO P&amp;L 65</t>
-  </si>
-  <si>
-    <t>10037632</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST CKLT.65</t>
-  </si>
-  <si>
-    <t>10037640</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST VNILA65</t>
-  </si>
-  <si>
-    <t>20139460</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO HZL 108</t>
-  </si>
-  <si>
-    <t>20140087</t>
-  </si>
-  <si>
-    <t>WALLS FEAST MAX CHO</t>
-  </si>
-  <si>
-    <t>20141200</t>
-  </si>
-  <si>
-    <t>WALLS BALL STRW GUAV</t>
-  </si>
-  <si>
-    <t>20141201</t>
-  </si>
-  <si>
-    <t>WALLS BALL GRAPE</t>
-  </si>
-  <si>
-    <t>20129821</t>
-  </si>
-  <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
-  </si>
-  <si>
-    <t>20032368</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM ALMD80</t>
-  </si>
-  <si>
-    <t>20032366</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM CLAS80</t>
-  </si>
-  <si>
-    <t>20134689</t>
-  </si>
-  <si>
-    <t>MAGNUM MNGO YOGHRT80</t>
-  </si>
-  <si>
-    <t>20138475</t>
-  </si>
-  <si>
-    <t>WALLS MGNUM STRW PAN</t>
-  </si>
-  <si>
-    <t>20054385</t>
-  </si>
-  <si>
-    <t>WALLS NEO EXT.CRM350</t>
-  </si>
-  <si>
     <t>20137108</t>
   </si>
   <si>
@@ -295,12 +352,18 @@
     <t>MAGNUM MINI CAS 6S</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20115639</t>
   </si>
   <si>
     <t>WALLS OREO VNL90</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>10005038</t>
   </si>
   <si>
@@ -329,9 +392,6 @@
   </si>
   <si>
     <t>CRNTTO RS CHO CHS134</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>20133149</t>
@@ -775,8 +835,8 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -911,10 +971,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -922,19 +982,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>19</v>
@@ -942,19 +1002,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -962,19 +1022,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>19</v>
@@ -982,19 +1042,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>19</v>
@@ -1002,19 +1062,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>19</v>
@@ -1022,19 +1082,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>19</v>
@@ -1042,19 +1102,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>19</v>
@@ -1062,19 +1122,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>19</v>
@@ -1082,19 +1142,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>19</v>
@@ -1102,19 +1162,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>19</v>
@@ -1122,19 +1182,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>19</v>
@@ -1142,19 +1202,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>19</v>
@@ -1162,19 +1222,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
@@ -1182,19 +1242,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
@@ -1202,19 +1262,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1222,19 +1282,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1242,19 +1302,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>19</v>
@@ -1262,19 +1322,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>19</v>
@@ -1282,19 +1342,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>19</v>
@@ -1302,19 +1362,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>19</v>
@@ -1322,19 +1382,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>19</v>
@@ -1342,19 +1402,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1362,19 +1422,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1382,19 +1442,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>19</v>
@@ -1402,19 +1462,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1422,19 +1482,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1442,19 +1502,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -1462,19 +1522,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1482,19 +1542,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1502,19 +1562,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -1522,19 +1582,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>19</v>
@@ -1542,19 +1602,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>15</v>
@@ -1562,19 +1622,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1582,19 +1642,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>19</v>
@@ -1602,19 +1662,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1622,19 +1682,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1642,19 +1702,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1662,19 +1722,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1682,19 +1742,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>19</v>
@@ -1702,19 +1762,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>19</v>
@@ -1722,19 +1782,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1742,19 +1802,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1762,19 +1822,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -1782,19 +1842,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -1802,19 +1862,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -1822,19 +1882,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>19</v>
@@ -1842,22 +1902,22 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="149">
   <si>
     <t/>
   </si>
@@ -271,6 +271,15 @@
     <t>30</t>
   </si>
   <si>
+    <t>20142871</t>
+  </si>
+  <si>
+    <t>WALL'S STRW CHS 350</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
     <t>20032368</t>
   </si>
   <si>
@@ -428,6 +437,18 @@
   </si>
   <si>
     <t>WALLS CALIPPO RED100</t>
+  </si>
+  <si>
+    <t>20142873</t>
+  </si>
+  <si>
+    <t>WALLS PPL LYC YGRT90</t>
+  </si>
+  <si>
+    <t>20142874</t>
+  </si>
+  <si>
+    <t>MAGNUM MINI CAP 6'S</t>
   </si>
   <si>
     <t>20134929</t>
@@ -829,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1411,21 +1432,21 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1434,7 +1455,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1442,10 +1463,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1454,18 +1475,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1474,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1482,10 +1503,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1494,10 +1515,10 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1514,18 +1535,18 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1534,7 +1555,7 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1542,10 +1563,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1554,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1562,10 +1583,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1574,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -1582,10 +1603,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1594,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>19</v>
@@ -1602,10 +1623,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1614,18 +1635,18 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1634,18 +1655,18 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1654,10 +1675,10 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1677,7 +1698,7 @@
         <v>116</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1694,7 +1715,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1702,10 +1723,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1714,7 +1735,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1722,10 +1743,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1734,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1742,10 +1763,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1754,18 +1775,18 @@
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1774,7 +1795,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>19</v>
@@ -1782,10 +1803,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1794,7 +1815,7 @@
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1802,10 +1823,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1814,7 +1835,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1822,10 +1843,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -1834,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -1842,10 +1863,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -1854,7 +1875,7 @@
         <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -1862,10 +1883,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -1874,18 +1895,18 @@
         <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -1894,18 +1915,18 @@
         <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -1914,10 +1935,70 @@
         <v>8</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>141</v>
+      <c r="F55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="152">
   <si>
     <t/>
   </si>
@@ -458,6 +458,15 @@
   </si>
   <si>
     <t>RT</t>
+  </si>
+  <si>
+    <t>20143293</t>
+  </si>
+  <si>
+    <t>WALL FST POP COOKIES</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
 </sst>
 </file>
@@ -850,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2001,6 +2010,26 @@
         <v>148</v>
       </c>
     </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="141">
   <si>
     <t/>
   </si>
@@ -91,246 +91,234 @@
     <t>8</t>
   </si>
   <si>
-    <t>20136404</t>
-  </si>
-  <si>
-    <t>WALLS TWST GRP LYC55</t>
+    <t>20136702</t>
+  </si>
+  <si>
+    <t>MAGNUM CF.AU LAIT 80</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20140723</t>
+  </si>
+  <si>
+    <t>PADDLE POP FRT TOWER</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20140366</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO LAVA 65</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20142129</t>
+  </si>
+  <si>
+    <t>CORNETTO MATCHA STRW</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20137106</t>
+  </si>
+  <si>
+    <t>PADDLE POP JG.JLY 60</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20138191</t>
+  </si>
+  <si>
+    <t>WALL FST POP STR</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20140730</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO BROWNIE</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20141544</t>
+  </si>
+  <si>
+    <t>WALLS CLP PEACHMG100</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20141545</t>
+  </si>
+  <si>
+    <t>WALLS CLP STWPINE100</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20134926</t>
+  </si>
+  <si>
+    <t>WALL ICE CRM OREO 80</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20125168</t>
+  </si>
+  <si>
+    <t>WALL FST POP VN&amp;CR64</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20139189</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO P&amp;L 65</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10037632</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST CKLT.65</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10037640</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST VNILA65</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20139460</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO HZL 108</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20140087</t>
+  </si>
+  <si>
+    <t>WALLS FEAST MAX CHO</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20141200</t>
+  </si>
+  <si>
+    <t>WALLS BALL STRW GUAV</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20141201</t>
+  </si>
+  <si>
+    <t>WALLS BALL GRAPE</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20129821</t>
+  </si>
+  <si>
+    <t>MAGNUM MATCHA.CRBL80</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20142871</t>
+  </si>
+  <si>
+    <t>WALL'S STRW CHS 350</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20032368</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM ALMD80</t>
+  </si>
+  <si>
+    <t>20032366</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM CLAS80</t>
+  </si>
+  <si>
+    <t>20134689</t>
+  </si>
+  <si>
+    <t>MAGNUM MNGO YOGHRT80</t>
+  </si>
+  <si>
+    <t>20138475</t>
+  </si>
+  <si>
+    <t>WALLS MGNUM STRW PAN</t>
+  </si>
+  <si>
+    <t>20054385</t>
+  </si>
+  <si>
+    <t>WALLS NEO EXT.CRM350</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20140732</t>
+  </si>
+  <si>
+    <t>WALLS MATCHA STW 350</t>
+  </si>
+  <si>
+    <t>20138583</t>
+  </si>
+  <si>
+    <t>WALLS OREO MINI 6S</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20136702</t>
-  </si>
-  <si>
-    <t>MAGNUM CF.AU LAIT 80</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20140723</t>
-  </si>
-  <si>
-    <t>PADDLE POP FRT TOWER</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20140366</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO LAVA 65</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20142129</t>
-  </si>
-  <si>
-    <t>CORNETTO MATCHA STRW</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20137106</t>
-  </si>
-  <si>
-    <t>PADDLE POP JG.JLY 60</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20138191</t>
-  </si>
-  <si>
-    <t>WALL FST POP STR</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20140730</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO BROWNIE</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20141544</t>
-  </si>
-  <si>
-    <t>WALLS CLP PEACHMG100</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20141545</t>
-  </si>
-  <si>
-    <t>WALLS CLP STWPINE100</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20134926</t>
-  </si>
-  <si>
-    <t>WALL ICE CRM OREO 80</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20125168</t>
-  </si>
-  <si>
-    <t>WALL FST POP VN&amp;CR64</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20139189</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO P&amp;L 65</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>10037632</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST CKLT.65</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>10037640</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST VNILA65</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20139460</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO HZL 108</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20140087</t>
-  </si>
-  <si>
-    <t>WALLS FEAST MAX CHO</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20141200</t>
-  </si>
-  <si>
-    <t>WALLS BALL STRW GUAV</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20141201</t>
-  </si>
-  <si>
-    <t>WALLS BALL GRAPE</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20129821</t>
-  </si>
-  <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20142871</t>
-  </si>
-  <si>
-    <t>WALL'S STRW CHS 350</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20032368</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM ALMD80</t>
-  </si>
-  <si>
-    <t>20032366</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM CLAS80</t>
-  </si>
-  <si>
-    <t>20134689</t>
-  </si>
-  <si>
-    <t>MAGNUM MNGO YOGHRT80</t>
-  </si>
-  <si>
-    <t>20138475</t>
-  </si>
-  <si>
-    <t>WALLS MGNUM STRW PAN</t>
-  </si>
-  <si>
-    <t>20054385</t>
-  </si>
-  <si>
-    <t>WALLS NEO EXT.CRM350</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20137108</t>
-  </si>
-  <si>
-    <t>WALLS TROPCL DL 350</t>
-  </si>
-  <si>
-    <t>20140732</t>
-  </si>
-  <si>
-    <t>WALLS MATCHA STW 350</t>
-  </si>
-  <si>
-    <t>20138583</t>
-  </si>
-  <si>
-    <t>WALLS OREO MINI 6S</t>
-  </si>
-  <si>
     <t>20136391</t>
   </si>
   <si>
@@ -355,15 +343,6 @@
     <t>WALL MN CORNT TR&amp;D/C</t>
   </si>
   <si>
-    <t>20138847</t>
-  </si>
-  <si>
-    <t>MAGNUM MINI CAS 6S</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20115639</t>
   </si>
   <si>
@@ -413,18 +392,6 @@
   </si>
   <si>
     <t>CRNETTO YGRT BRY 108</t>
-  </si>
-  <si>
-    <t>20134533</t>
-  </si>
-  <si>
-    <t>PADDLE POP MINION 42</t>
-  </si>
-  <si>
-    <t>20138193</t>
-  </si>
-  <si>
-    <t>CRNETO APLE CRMBL108</t>
   </si>
   <si>
     <t>20094824</t>
@@ -859,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1287,7 +1254,7 @@
         <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1327,7 +1294,7 @@
         <v>70</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1441,22 +1408,22 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1464,7 +1431,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1472,11 +1439,11 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
@@ -1484,19 +1451,19 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
@@ -1504,7 +1471,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1512,22 +1479,22 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,27 +1511,27 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1584,7 +1551,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1604,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -1624,10 +1591,10 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,10 +1611,10 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,18 +1631,18 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1692,10 +1659,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1704,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,7 +1691,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1732,11 +1699,11 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
@@ -1744,19 +1711,19 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
@@ -1764,19 +1731,19 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
@@ -1784,19 +1751,19 @@
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
@@ -1804,7 +1771,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>19</v>
@@ -1812,11 +1779,11 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
@@ -1824,19 +1791,19 @@
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
@@ -1844,7 +1811,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1852,11 +1819,11 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
@@ -1864,7 +1831,7 @@
         <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -1872,11 +1839,11 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
@@ -1884,7 +1851,7 @@
         <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -1892,22 +1859,22 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,109 +1891,9 @@
         <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F58" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -430,7 +430,7 @@
     <t>20143293</t>
   </si>
   <si>
-    <t>WALL FST POP COOKIES</t>
+    <t>WALS FST POP CKIES64</t>
   </si>
   <si>
     <t>32</t>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="146">
   <si>
     <t/>
   </si>
@@ -271,6 +271,24 @@
     <t>31</t>
   </si>
   <si>
+    <t>20143879</t>
+  </si>
+  <si>
+    <t>WALS SLRO GRP APLE62</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20143878</t>
+  </si>
+  <si>
+    <t>WLS CRNETO MLKSHAK80</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
     <t>20032368</t>
   </si>
   <si>
@@ -431,9 +449,6 @@
   </si>
   <si>
     <t>WALS FST POP CKIES64</t>
-  </si>
-  <si>
-    <t>32</t>
   </si>
 </sst>
 </file>
@@ -826,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1408,41 +1423,41 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1451,18 +1466,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1471,18 +1486,18 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1491,18 +1506,18 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1511,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -1519,10 +1534,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1531,18 +1546,18 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1551,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1559,10 +1574,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1571,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -1579,10 +1594,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1591,18 +1606,18 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1611,18 +1626,18 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1631,18 +1646,18 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1651,7 +1666,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1659,10 +1674,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1671,7 +1686,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1679,10 +1694,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1691,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1699,10 +1714,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1711,18 +1726,18 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1731,18 +1746,18 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1751,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>19</v>
@@ -1759,10 +1774,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1771,7 +1786,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>19</v>
@@ -1779,10 +1794,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1791,18 +1806,18 @@
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1811,7 +1826,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>19</v>
@@ -1819,10 +1834,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -1831,18 +1846,18 @@
         <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -1851,7 +1866,7 @@
         <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -1859,10 +1874,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -1871,18 +1886,18 @@
         <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -1891,9 +1906,49 @@
         <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>19</v>
       </c>
     </row>
